--- a/mode_docx_gen/pmi_mtz/bnt_modes/БНТ_7.xlsx
+++ b/mode_docx_gen/pmi_mtz/bnt_modes/БНТ_7.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="28725" windowHeight="10815" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SGF_Parameters" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,25 +13,20 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Outputs" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,32 +41,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor rgb="FFFF0000"/>
+        <fgColor rgb="00FF0000"/>
+        <bgColor rgb="00FF0000"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -83,18 +64,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -460,7 +438,53 @@
   <dimension ref="A1:AU2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="47"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
+    <col width="20" customWidth="1" min="26" max="26"/>
+    <col width="20" customWidth="1" min="27" max="27"/>
+    <col width="20" customWidth="1" min="28" max="28"/>
+    <col width="20" customWidth="1" min="29" max="29"/>
+    <col width="20" customWidth="1" min="30" max="30"/>
+    <col width="20" customWidth="1" min="31" max="31"/>
+    <col width="20" customWidth="1" min="32" max="32"/>
+    <col width="20" customWidth="1" min="33" max="33"/>
+    <col width="20" customWidth="1" min="34" max="34"/>
+    <col width="20" customWidth="1" min="35" max="35"/>
+    <col width="20" customWidth="1" min="36" max="36"/>
+    <col width="20" customWidth="1" min="37" max="37"/>
+    <col width="20" customWidth="1" min="38" max="38"/>
+    <col width="20" customWidth="1" min="39" max="39"/>
+    <col width="20" customWidth="1" min="40" max="40"/>
+    <col width="20" customWidth="1" min="41" max="41"/>
+    <col width="20" customWidth="1" min="42" max="42"/>
+    <col width="20" customWidth="1" min="43" max="43"/>
+    <col width="20" customWidth="1" min="44" max="44"/>
+    <col width="20" customWidth="1" min="45" max="45"/>
+    <col width="20" customWidth="1" min="46" max="46"/>
+    <col width="20" customWidth="1" min="47" max="47"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -773,44 +797,44 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
-      <c r="Y2" s="2" t="n">
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
+      <c r="AF2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -856,176 +880,199 @@
   </sheetPr>
   <dimension ref="A1:U2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>T1_ptoc1_lvttoc</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Iset_ptoc1_lvttoc</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Icoarse_ptoc1_lvttoc</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>T1_ptoc2_lvttoc</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Iset_ptoc2_lvttoc</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Icoarse_ptoc2_lvttoc</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>T1_ptoc3_lvttoc</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Iset_ptoc3_lvttoc</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Icoarse_ptoc3_lvttoc</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Uop_ptuv1_lvttoc</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>U2op_ptuv1_lvttoc</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Uop_ptuv2_lvttoc</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>U2op_ptuv2_lvttoc</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Imax_phar1_lvttoc</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Ratio_phar1_lvttoc</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Umin_lvrbvtr1</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>U2max_lvrbvtr1</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>T1_lvrbvtr1</t>
         </is>
       </c>
-      <c r="S1" s="3" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Umin_lvrbvtr2</t>
         </is>
       </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>U2max_lvrbvtr2</t>
         </is>
       </c>
-      <c r="U1" s="3" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>T1_lvrbvtr2</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="O2" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="K2" t="n">
-        <v>5</v>
-      </c>
-      <c r="L2" t="n">
-        <v>40</v>
-      </c>
-      <c r="M2" t="n">
-        <v>5</v>
-      </c>
-      <c r="N2" t="n">
-        <v>5</v>
-      </c>
-      <c r="O2" t="n">
-        <v>40</v>
-      </c>
-      <c r="P2" t="n">
-        <v>40</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>5</v>
-      </c>
-      <c r="R2" t="n">
+      <c r="P2" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="R2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="S2" t="n">
-        <v>40</v>
-      </c>
-      <c r="T2" t="n">
-        <v>5</v>
-      </c>
-      <c r="U2" t="n">
+      <c r="S2" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="U2" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1040,10 +1087,52 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM2"/>
+  <dimension ref="A1:AQ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="39"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
+    <col width="20" customWidth="1" min="26" max="26"/>
+    <col width="20" customWidth="1" min="27" max="27"/>
+    <col width="20" customWidth="1" min="28" max="28"/>
+    <col width="20" customWidth="1" min="29" max="29"/>
+    <col width="20" customWidth="1" min="30" max="30"/>
+    <col width="20" customWidth="1" min="31" max="31"/>
+    <col width="20" customWidth="1" min="32" max="32"/>
+    <col width="20" customWidth="1" min="33" max="33"/>
+    <col width="20" customWidth="1" min="34" max="34"/>
+    <col width="20" customWidth="1" min="35" max="35"/>
+    <col width="20" customWidth="1" min="36" max="36"/>
+    <col width="20" customWidth="1" min="37" max="37"/>
+    <col width="20" customWidth="1" min="38" max="38"/>
+    <col width="20" customWidth="1" min="39" max="39"/>
+    <col width="20" customWidth="1" min="40" max="40"/>
+    <col width="20" customWidth="1" min="41" max="41"/>
+    <col width="20" customWidth="1" min="42" max="42"/>
+    <col width="20" customWidth="1" min="43" max="43"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1104,140 +1193,160 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>dIA</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>IB</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>dIB</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>IC</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>IAB</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>IBC</t>
-        </is>
-      </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>dIC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>UAB_ptuv1</t>
+          <t>UA1</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>UBC_ptuv1</t>
+          <t>dUA1</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>UCA_ptuv1</t>
+          <t>UB1</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>U2_ptuv1</t>
+          <t>dUB1</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>UAB_ptuv2</t>
+          <t>UC1</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>UBC_ptuv2</t>
+          <t>dUC1</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>UCA_ptuv2</t>
+          <t>UA2</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>U2_ptuv2</t>
+          <t>dUA2</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
+          <t>UB2</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dUB2</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>UC2</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dUC2</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>KPONvnesh_ptuv1</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>KPONvnesh_ptuv2</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>IA2harm</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>IB2harm</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>IC2harm</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>VNN1vkl</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>VNN2vkl</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>OV_lvrbvtr1</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>vnesh_bnn_srab_lvrbvtr1</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>OV_lvrbvtr2</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>vnesh_bnn_srab_lvrbvtr2</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>OVlot</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>OVlo</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>OVzapv</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>OVzavr</t>
         </is>
@@ -1275,58 +1384,58 @@
         <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
+      <c r="M2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>58</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
+      <c r="S2" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="W2" s="2" t="n">
+        <v>58</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
+      <c r="Y2" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z2" s="2" t="n">
+        <v>240</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
+        <v>58</v>
+      </c>
+      <c r="AB2" s="2" t="n">
+        <v>120</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -1337,8 +1446,8 @@
       <c r="AE2" t="n">
         <v>0</v>
       </c>
-      <c r="AF2" t="n">
-        <v>0</v>
+      <c r="AF2" s="2" t="n">
+        <v>100</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -1359,6 +1468,18 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1373,10 +1494,94 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL2"/>
+  <dimension ref="A1:CG2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="64"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
+    <col width="20" customWidth="1" min="26" max="26"/>
+    <col width="20" customWidth="1" min="27" max="27"/>
+    <col width="20" customWidth="1" min="28" max="28"/>
+    <col width="20" customWidth="1" min="29" max="29"/>
+    <col width="20" customWidth="1" min="30" max="30"/>
+    <col width="20" customWidth="1" min="31" max="31"/>
+    <col width="20" customWidth="1" min="32" max="32"/>
+    <col width="20" customWidth="1" min="33" max="33"/>
+    <col width="20" customWidth="1" min="34" max="34"/>
+    <col width="20" customWidth="1" min="35" max="35"/>
+    <col width="20" customWidth="1" min="36" max="36"/>
+    <col width="20" customWidth="1" min="37" max="37"/>
+    <col width="20" customWidth="1" min="38" max="38"/>
+    <col width="20" customWidth="1" min="39" max="39"/>
+    <col width="20" customWidth="1" min="40" max="40"/>
+    <col width="20" customWidth="1" min="41" max="41"/>
+    <col width="20" customWidth="1" min="42" max="42"/>
+    <col width="20" customWidth="1" min="43" max="43"/>
+    <col width="20" customWidth="1" min="44" max="44"/>
+    <col width="20" customWidth="1" min="45" max="45"/>
+    <col width="20" customWidth="1" min="46" max="46"/>
+    <col width="20" customWidth="1" min="47" max="47"/>
+    <col width="20" customWidth="1" min="48" max="48"/>
+    <col width="20" customWidth="1" min="49" max="49"/>
+    <col width="20" customWidth="1" min="50" max="50"/>
+    <col width="20" customWidth="1" min="51" max="51"/>
+    <col width="20" customWidth="1" min="52" max="52"/>
+    <col width="20" customWidth="1" min="53" max="53"/>
+    <col width="20" customWidth="1" min="54" max="54"/>
+    <col width="20" customWidth="1" min="55" max="55"/>
+    <col width="20" customWidth="1" min="56" max="56"/>
+    <col width="20" customWidth="1" min="57" max="57"/>
+    <col width="20" customWidth="1" min="58" max="58"/>
+    <col width="20" customWidth="1" min="59" max="59"/>
+    <col width="20" customWidth="1" min="60" max="60"/>
+    <col width="20" customWidth="1" min="61" max="61"/>
+    <col width="20" customWidth="1" min="62" max="62"/>
+    <col width="20" customWidth="1" min="63" max="63"/>
+    <col width="20" customWidth="1" min="64" max="64"/>
+    <col width="20" customWidth="1" min="65" max="65"/>
+    <col width="20" customWidth="1" min="66" max="66"/>
+    <col width="20" customWidth="1" min="67" max="67"/>
+    <col width="20" customWidth="1" min="68" max="68"/>
+    <col width="20" customWidth="1" min="69" max="69"/>
+    <col width="20" customWidth="1" min="70" max="70"/>
+    <col width="20" customWidth="1" min="71" max="71"/>
+    <col width="20" customWidth="1" min="72" max="72"/>
+    <col width="20" customWidth="1" min="73" max="73"/>
+    <col width="20" customWidth="1" min="74" max="74"/>
+    <col width="20" customWidth="1" min="75" max="75"/>
+    <col width="20" customWidth="1" min="76" max="76"/>
+    <col width="20" customWidth="1" min="77" max="77"/>
+    <col width="20" customWidth="1" min="78" max="78"/>
+    <col width="20" customWidth="1" min="79" max="79"/>
+    <col width="20" customWidth="1" min="80" max="80"/>
+    <col width="20" customWidth="1" min="81" max="81"/>
+    <col width="20" customWidth="1" min="82" max="82"/>
+    <col width="20" customWidth="1" min="83" max="83"/>
+    <col width="20" customWidth="1" min="84" max="84"/>
+    <col width="20" customWidth="1" min="85" max="85"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1700,6 +1905,111 @@
           <t>pusk_lvalv</t>
         </is>
       </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>IAB</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>dIAB</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>IBC</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>dIBC</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>dICA</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>I2</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>I0</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>I1</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>UAB_ptuv1</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>UBC_ptuv1</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>UCA_ptuv1</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>U2_ptuv1</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>U0_ptuv1</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>U1_ptuv1</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>UAB_ptuv2</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>UBC_ptuv2</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>UCA_ptuv2</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>U2_ptuv2</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>U0_ptuv2</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>U1_ptuv2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1827,9 +2137,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -1837,24 +2147,24 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AF2" s="2" t="inlineStr">
@@ -1862,14 +2172,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="AG2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -1937,41 +2247,41 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AV2" s="2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AW2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AW2" s="2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AX2" s="2" t="inlineStr">
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BA2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AY2" s="2" t="inlineStr">
+      <c r="BB2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BC2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1982,14 +2292,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="BE2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1997,14 +2307,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="BH2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BI2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -2012,14 +2322,119 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BM2" s="2" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="BN2" s="2" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="BO2" s="2" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="BP2" s="2" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="BQ2" s="2" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="BR2" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BU2" s="2" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="BV2" s="2" t="inlineStr">
+        <is>
+          <t>100.46</t>
+        </is>
+      </c>
+      <c r="BW2" s="2" t="inlineStr">
+        <is>
+          <t>100.46</t>
+        </is>
+      </c>
+      <c r="BX2" s="2" t="inlineStr">
+        <is>
+          <t>100.46</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CA2" s="2" t="inlineStr">
+        <is>
+          <t>58.0</t>
+        </is>
+      </c>
+      <c r="CB2" s="2" t="inlineStr">
+        <is>
+          <t>100.46</t>
+        </is>
+      </c>
+      <c r="CC2" s="2" t="inlineStr">
+        <is>
+          <t>100.46</t>
+        </is>
+      </c>
+      <c r="CD2" s="2" t="inlineStr">
+        <is>
+          <t>100.46</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CG2" s="2" t="inlineStr">
+        <is>
+          <t>58.0</t>
         </is>
       </c>
     </row>

--- a/mode_docx_gen/pmi_mtz/bnt_modes/БНТ_7.xlsx
+++ b/mode_docx_gen/pmi_mtz/bnt_modes/БНТ_7.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU2"/>
+  <dimension ref="A1:AV2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -485,6 +485,7 @@
     <col width="20" customWidth="1" min="45" max="45"/>
     <col width="20" customWidth="1" min="46" max="46"/>
     <col width="20" customWidth="1" min="47" max="47"/>
+    <col width="20" customWidth="1" min="48" max="48"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -723,6 +724,11 @@
           <t>SGF10_lvalv</t>
         </is>
       </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>Номинальный ток входа</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -865,6 +871,9 @@
       </c>
       <c r="AU2" t="n">
         <v>0</v>
+      </c>
+      <c r="AV2" s="2" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1016,61 +1025,61 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N2" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="N2" s="2" t="n">
-        <v>5</v>
       </c>
       <c r="O2" s="2" t="n">
         <v>40</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="U2" s="2" t="n">
         <v>1</v>

--- a/mode_docx_gen/pmi_mtz/bnt_modes/БНТ_7.xlsx
+++ b/mode_docx_gen/pmi_mtz/bnt_modes/БНТ_7.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV2"/>
+  <dimension ref="A1:BA2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -486,6 +486,11 @@
     <col width="20" customWidth="1" min="46" max="46"/>
     <col width="20" customWidth="1" min="47" max="47"/>
     <col width="20" customWidth="1" min="48" max="48"/>
+    <col width="20" customWidth="1" min="49" max="49"/>
+    <col width="20" customWidth="1" min="50" max="50"/>
+    <col width="20" customWidth="1" min="51" max="51"/>
+    <col width="20" customWidth="1" min="52" max="52"/>
+    <col width="20" customWidth="1" min="53" max="53"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -676,55 +681,80 @@
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_lvalv</t>
+          <t>SGF1_lvalh</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>SGF2_lvalv</t>
+          <t>SGF2_lvalh</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>SGF3_lvalv</t>
+          <t>SGF3_lvalh</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>SGF4_lvalv</t>
+          <t>SGF4_lvalh</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>SGF5_lvalv</t>
+          <t>SGF5_lvalh</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>SGF6_lvalv</t>
+          <t>SGF6_lvalh</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>SGF7_lvalv</t>
+          <t>SGF7_lvalh</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>SGF8_lvalv</t>
+          <t>SGF8_lvalh</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>SGF9_lvalv</t>
+          <t>SGF9_lvalh</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>SGF10_lvalv</t>
+          <t>SGF10_lvalh</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>SGF1_ptoc1_lvarctoc</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>SGF2_ptoc1_lvarctoc</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>SGF1_ptrc1_ttoclgc</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>SGF2_ptrc1_ttoclgc</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>SGF3_ptrc1_ttoclgc</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>Номинальный ток входа</t>
         </is>
@@ -872,7 +902,22 @@
       <c r="AU2" t="n">
         <v>0</v>
       </c>
-      <c r="AV2" s="2" t="n">
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -887,7 +932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -911,6 +956,7 @@
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
     <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1019,6 +1065,11 @@
           <t>T1_lvrbvtr2</t>
         </is>
       </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Iset_ptoc1_lvarctoc</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -1082,6 +1133,9 @@
         <v>5</v>
       </c>
       <c r="U2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1456,7 +1510,7 @@
         <v>0</v>
       </c>
       <c r="AF2" s="2" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -1503,7 +1557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG2"/>
+  <dimension ref="A1:CI2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1591,6 +1645,8 @@
     <col width="20" customWidth="1" min="83" max="83"/>
     <col width="20" customWidth="1" min="84" max="84"/>
     <col width="20" customWidth="1" min="85" max="85"/>
+    <col width="20" customWidth="1" min="86" max="86"/>
+    <col width="20" customWidth="1" min="87" max="87"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1911,110 +1967,120 @@
       </c>
       <c r="BL1" s="1" t="inlineStr">
         <is>
-          <t>pusk_lvalv</t>
+          <t>pusk_lvalh</t>
         </is>
       </c>
       <c r="BM1" s="1" t="inlineStr">
         <is>
+          <t>pusk_ptoc1_lvarctoc</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>pusk_ptrc1_ttoclgc</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
           <t>IAB</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>dIAB</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>IBC</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>dIBC</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>ICA</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>dICA</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>I2</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>I0</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>I1</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>UAB_ptuv1</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>UBC_ptuv1</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>UCA_ptuv1</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>U2_ptuv1</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>U0_ptuv1</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>U1_ptuv1</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>UAB_ptuv2</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>UBC_ptuv2</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>UCA_ptuv2</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>U2_ptuv2</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>U0_ptuv2</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>U1_ptuv2</t>
         </is>
@@ -2341,107 +2407,117 @@
           <t>1</t>
         </is>
       </c>
-      <c r="BM2" s="2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BO2" s="2" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="BN2" s="2" t="inlineStr">
+      <c r="BP2" s="2" t="inlineStr">
         <is>
           <t>30.0</t>
         </is>
       </c>
-      <c r="BO2" s="2" t="inlineStr">
+      <c r="BQ2" s="2" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="BP2" s="2" t="inlineStr">
+      <c r="BR2" s="2" t="inlineStr">
         <is>
           <t>-90.0</t>
         </is>
       </c>
-      <c r="BQ2" s="2" t="inlineStr">
+      <c r="BS2" s="2" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="BR2" s="2" t="inlineStr">
+      <c r="BT2" s="2" t="inlineStr">
         <is>
           <t>150.0</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="BU2" s="2" t="inlineStr">
+      <c r="BW2" s="2" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="BV2" s="2" t="inlineStr">
+      <c r="BX2" s="2" t="inlineStr">
         <is>
           <t>100.46</t>
         </is>
       </c>
-      <c r="BW2" s="2" t="inlineStr">
+      <c r="BY2" s="2" t="inlineStr">
         <is>
           <t>100.46</t>
         </is>
       </c>
-      <c r="BX2" s="2" t="inlineStr">
+      <c r="BZ2" s="2" t="inlineStr">
         <is>
           <t>100.46</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
+      <c r="CA2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CA2" s="2" t="inlineStr">
+      <c r="CC2" s="2" t="inlineStr">
         <is>
           <t>58.0</t>
         </is>
       </c>
-      <c r="CB2" s="2" t="inlineStr">
+      <c r="CD2" s="2" t="inlineStr">
         <is>
           <t>100.46</t>
         </is>
       </c>
-      <c r="CC2" s="2" t="inlineStr">
+      <c r="CE2" s="2" t="inlineStr">
         <is>
           <t>100.46</t>
         </is>
       </c>
-      <c r="CD2" s="2" t="inlineStr">
+      <c r="CF2" s="2" t="inlineStr">
         <is>
           <t>100.46</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CG2" s="2" t="inlineStr">
+      <c r="CI2" s="2" t="inlineStr">
         <is>
           <t>58.0</t>
         </is>
